--- a/artfynd/A 48549-2025 artfynd.xlsx
+++ b/artfynd/A 48549-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136907566</v>
       </c>
       <c r="B2" t="n">
-        <v>58000</v>
+        <v>58013</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48549-2025 artfynd.xlsx
+++ b/artfynd/A 48549-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136907566</v>
       </c>
       <c r="B2" t="n">
-        <v>58013</v>
+        <v>58015</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48549-2025 artfynd.xlsx
+++ b/artfynd/A 48549-2025 artfynd.xlsx
@@ -715,11 +715,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>

--- a/artfynd/A 48549-2025 artfynd.xlsx
+++ b/artfynd/A 48549-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136907566</v>
       </c>
       <c r="B2" t="n">
-        <v>58015</v>
+        <v>58025</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48549-2025 artfynd.xlsx
+++ b/artfynd/A 48549-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136907566</v>
       </c>
       <c r="B2" t="n">
-        <v>58025</v>
+        <v>58026</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48549-2025 artfynd.xlsx
+++ b/artfynd/A 48549-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136907566</v>
       </c>
       <c r="B2" t="n">
-        <v>58026</v>
+        <v>58027</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
